--- a/data/output/resultados.xlsx
+++ b/data/output/resultados.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Flujos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resultados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Flujos'!$A$1:$AL$23</definedName>
@@ -61,12 +61,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3671,153 +3673,147 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Escenario</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>VEP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Delta VEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Delta VEP %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VEP Base</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>248344010.9633576</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VEP Paralelo Arriba</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>Paralelo Arriba</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>247930118.4354009</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>413892.5279567242</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.001666609661135709</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VEP Paralelo Abajo</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+          <t>Paralelo Abajo</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>248758594.4401422</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-414583.4767845273</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>-0.001669391885780961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VEP Empinamiento</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+          <t>Empinamiento</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>248672472.7110089</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-328461.7476513088</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-0.001322607887249483</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VEP Aplanamiento</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+          <t>Aplanamiento</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>247937624.014855</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>406386.9485026598</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.001636387150735924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VEP Corto Arriba</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+          <t>Corto Arriba</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>247832111.9990593</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>511898.9642983675</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.002061249483378508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VEP Corto Abajo</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+          <t>Corto Abajo</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>248856967.2585546</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Delta VEP Paralelo Arriba</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>413892.5279567242</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Delta VEP Paralelo Abajo</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-414583.4767845273</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Delta VEP Empinamiento</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-328461.7476513088</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Delta VEP Aplanamiento</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>406386.9485026598</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Delta VEP Corto Arriba</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>511898.9642983675</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Delta VEP Corto Abajo</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+      <c r="C8" s="3" t="n">
         <v>-512956.2951969504</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-0.002065507008633422</v>
       </c>
     </row>
   </sheetData>
